--- a/assets/constructions/examples/ctd_jdi.xlsx
+++ b/assets/constructions/examples/ctd_jdi.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,11 +624,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2650-1644 6g ХВСГ ГОСТ 9740-71</t>
+          <t>2650-1423 6g Р6М3 ГОСТ 9740-71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -639,12 +664,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -654,7 +679,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -666,35 +691,35 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>M8x0,5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -704,12 +729,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>DIE_ROUND:25</t>
+          <t>DIE_ROUND:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -726,12 +751,12 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>ХВСГ</t>
+          <t>Р6М3</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
@@ -753,13 +778,24 @@
       <c r="AM2" t="inlineStr">
         <is>
           <t>ГОСТ 9740-71</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2650-1406 6g 13Х ГОСТ 9740-71</t>
+          <t>2650-1346 6g Р9 ГОСТ 9740-71</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -775,7 +811,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -797,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
         <v>16</v>
@@ -805,17 +841,17 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>M1,8</t>
+          <t>M1,2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -857,12 +893,12 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13Х</t>
+          <t>Р9</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -884,13 +920,24 @@
       <c r="AM3" t="inlineStr">
         <is>
           <t>ГОСТ 9740-71</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>PKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2650-2844 6g 13Х ГОСТ 9740-71</t>
+          <t>2650-2017 6g У11А ГОСТ 9740-71</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -906,7 +953,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -928,25 +975,25 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>M56x4</t>
+          <t>M15x1,5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -956,7 +1003,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -966,12 +1013,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>DIE_ROUND:105</t>
+          <t>DIE_ROUND:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +1035,7 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13Х</t>
+          <t>У11А</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1015,13 +1062,24 @@
       <c r="AM4" t="inlineStr">
         <is>
           <t>ГОСТ 9740-71</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>PMN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2650-2356 6g У13А ГОСТ 9740-71</t>
+          <t>2650-2561 6g У7А ГОСТ 9740-71</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1037,7 +1095,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1059,25 +1117,25 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>M30x3</t>
+          <t>M40x1,5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -1087,7 +1145,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1097,12 +1155,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>DIE_ROUND:65</t>
+          <t>DIE_ROUND:75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1177,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>У13А</t>
+          <t>У7А</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1146,13 +1204,24 @@
       <c r="AM5" t="inlineStr">
         <is>
           <t>ГОСТ 9740-71</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2650-2448 6g У12А ГОСТ 9740-71</t>
+          <t>2650-2262 6g Х ГОСТ 9740-71</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1168,7 +1237,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1190,25 +1259,25 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>M33x0,75</t>
+          <t>M25x2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -1218,7 +1287,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1233,7 +1302,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>DIE_ROUND:65</t>
+          <t>DIE_ROUND:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1319,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>У12А</t>
+          <t>Х</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1277,6 +1346,17 @@
       <c r="AM6" t="inlineStr">
         <is>
           <t>ГОСТ 9740-71</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>PM</t>
         </is>
       </c>
     </row>
